--- a/data/processed/positivacao/2020-05_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2020-05_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -23905,7 +23905,7 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B907" t="inlineStr"/>
@@ -35179,7 +35179,7 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr"/>
@@ -64071,7 +64071,7 @@
     <row r="2453">
       <c r="A2453" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2453" t="inlineStr"/>
@@ -65768,12 +65768,12 @@
       <c r="A2519" t="inlineStr"/>
       <c r="B2519" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 91 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 91 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 10 cliente(s), não positivou 796 cliente(s) - Total vendido: R$ 4.186,22
-Vendedor 3 - FERNANDA: positivou 5 cliente(s), não positivou 428 cliente(s) - Total vendido: R$ 1.886,77
-Vendedor 4 - DANIELA: positivou 0 cliente(s), não positivou 656 cliente(s) - Total vendido: R$ 0,00
+Vendedor 3 - VENDEDOR 03: positivou 5 cliente(s), não positivou 428 cliente(s) - Total vendido: R$ 1.886,77
+Vendedor 4 - VENDEDOR 04: positivou 0 cliente(s), não positivou 656 cliente(s) - Total vendido: R$ 0,00
 Vendedor 5 - SITE: positivou 0 cliente(s), não positivou 454 cliente(s) - Total vendido: R$ 0,00
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 64 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 64 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2519" t="inlineStr"/>
